--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v1/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v1/Contrary(P)Body(N).xlsx
@@ -17283,16 +17283,16 @@
         <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.421053</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4933920704845814</v>
+        <v>0.493392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5436507936507936</v>
+        <v>0.543651</v>
       </c>
     </row>
     <row r="3">
@@ -17342,16 +17342,16 @@
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>0.417910447761194</v>
+        <v>0.41791</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4912280701754387</v>
+        <v>0.491228</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.539683</v>
       </c>
     </row>
     <row r="4">
@@ -17401,16 +17401,16 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.417910447761194</v>
+        <v>0.41791</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4912280701754387</v>
+        <v>0.491228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.539683</v>
       </c>
     </row>
   </sheetData>
